--- a/seguimiento/baranoa-dsmc7tar/cronograma-ejecutado.xlsx
+++ b/seguimiento/baranoa-dsmc7tar/cronograma-ejecutado.xlsx
@@ -1244,8 +1244,12 @@
       </c>
       <c r="O12" s="21" t="n"/>
       <c r="P12" s="21" t="n"/>
-      <c r="Q12" s="21" t="n"/>
-      <c r="R12" s="21" t="n"/>
+      <c r="Q12" s="21" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R12" s="21" t="n">
+        <v>0.25</v>
+      </c>
       <c r="S12" s="21" t="n"/>
       <c r="T12" s="21" t="n"/>
       <c r="U12" s="21" t="n"/>
@@ -1625,12 +1629,12 @@
       <c r="P19" s="21" t="n">
         <v>0.29</v>
       </c>
-      <c r="Q19" s="21" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="R19" s="21" t="n"/>
+      <c r="Q19" s="21" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="R19" s="21" t="n">
+        <v>0.28</v>
+      </c>
       <c r="S19" s="21" t="n"/>
       <c r="T19" s="21" t="n"/>
       <c r="U19" s="21" t="n"/>
@@ -1682,10 +1686,8 @@
           <t>P</t>
         </is>
       </c>
-      <c r="S20" s="21" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+      <c r="S20" s="21" t="n">
+        <v>0.35</v>
       </c>
       <c r="T20" s="21" t="inlineStr">
         <is>
@@ -1920,7 +1922,9 @@
       <c r="P24" s="21" t="n">
         <v>0.73</v>
       </c>
-      <c r="Q24" s="21" t="n"/>
+      <c r="Q24" s="21" t="n">
+        <v>0.27</v>
+      </c>
       <c r="R24" s="21" t="inlineStr">
         <is>
           <t>P</t>
@@ -2156,7 +2160,9 @@
       <c r="N28" s="21" t="n"/>
       <c r="O28" s="21" t="n"/>
       <c r="P28" s="21" t="n"/>
-      <c r="Q28" s="21" t="n"/>
+      <c r="Q28" s="21" t="n">
+        <v>0.3</v>
+      </c>
       <c r="R28" s="21" t="n"/>
       <c r="S28" s="21" t="n"/>
       <c r="T28" s="21" t="n"/>
@@ -3399,15 +3405,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="Q51" s="21" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
-      </c>
-      <c r="R51" s="21" t="inlineStr">
-        <is>
-          <t>P</t>
-        </is>
+      <c r="Q51" s="21" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="R51" s="21" t="n">
+        <v>0.13</v>
       </c>
       <c r="S51" s="21" t="n"/>
       <c r="T51" s="21" t="n"/>

--- a/seguimiento/baranoa-dsmc7tar/cronograma-ejecutado.xlsx
+++ b/seguimiento/baranoa-dsmc7tar/cronograma-ejecutado.xlsx
@@ -695,7 +695,7 @@
     <row r="5">
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>SEMANA DEL (LUNES)</t>
+          <t>SEMANA DEL</t>
         </is>
       </c>
       <c r="E5" s="10" t="n">
@@ -2164,7 +2164,9 @@
         <v>0.3</v>
       </c>
       <c r="R28" s="21" t="n"/>
-      <c r="S28" s="21" t="n"/>
+      <c r="S28" s="21" t="n">
+        <v>0.2600000000000001</v>
+      </c>
       <c r="T28" s="21" t="n"/>
       <c r="U28" s="21" t="n"/>
       <c r="V28" s="21" t="n"/>
@@ -3409,7 +3411,7 @@
         <v>0.04</v>
       </c>
       <c r="R51" s="21" t="n">
-        <v>0.13</v>
+        <v>0.21</v>
       </c>
       <c r="S51" s="21" t="n"/>
       <c r="T51" s="21" t="n"/>

--- a/seguimiento/baranoa-dsmc7tar/cronograma-ejecutado.xlsx
+++ b/seguimiento/baranoa-dsmc7tar/cronograma-ejecutado.xlsx
@@ -2164,9 +2164,7 @@
         <v>0.3</v>
       </c>
       <c r="R28" s="21" t="n"/>
-      <c r="S28" s="21" t="n">
-        <v>0.2600000000000001</v>
-      </c>
+      <c r="S28" s="21" t="n"/>
       <c r="T28" s="21" t="n"/>
       <c r="U28" s="21" t="n"/>
       <c r="V28" s="21" t="n"/>

--- a/seguimiento/baranoa-dsmc7tar/cronograma-ejecutado.xlsx
+++ b/seguimiento/baranoa-dsmc7tar/cronograma-ejecutado.xlsx
@@ -18,11 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="dd/mm"/>
-    <numFmt numFmtId="167" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="dd/mm"/>
+    <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
   <fonts count="8">
     <font>
@@ -127,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -150,7 +149,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -190,10 +189,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -698,79 +704,79 @@
           <t>SEMANA DEL</t>
         </is>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="26" t="n">
         <v>46216</v>
       </c>
-      <c r="F5" s="10" t="n">
+      <c r="F5" s="26" t="n">
         <v>46223</v>
       </c>
-      <c r="G5" s="10" t="n">
+      <c r="G5" s="26" t="n">
         <v>46230</v>
       </c>
-      <c r="H5" s="10" t="n">
+      <c r="H5" s="26" t="n">
         <v>46237</v>
       </c>
-      <c r="I5" s="10" t="n">
+      <c r="I5" s="26" t="n">
         <v>46244</v>
       </c>
-      <c r="J5" s="10" t="n">
+      <c r="J5" s="26" t="n">
         <v>46251</v>
       </c>
-      <c r="K5" s="10" t="n">
+      <c r="K5" s="26" t="n">
         <v>46258</v>
       </c>
-      <c r="L5" s="10" t="n">
+      <c r="L5" s="26" t="n">
         <v>46265</v>
       </c>
-      <c r="M5" s="10" t="n">
+      <c r="M5" s="26" t="n">
         <v>46272</v>
       </c>
-      <c r="N5" s="10" t="n">
+      <c r="N5" s="26" t="n">
         <v>46279</v>
       </c>
-      <c r="O5" s="10" t="n">
+      <c r="O5" s="26" t="n">
         <v>46286</v>
       </c>
-      <c r="P5" s="10" t="n">
+      <c r="P5" s="26" t="n">
         <v>46293</v>
       </c>
-      <c r="Q5" s="10" t="n">
+      <c r="Q5" s="26" t="n">
         <v>46300</v>
       </c>
-      <c r="R5" s="10" t="n">
+      <c r="R5" s="26" t="n">
         <v>46307</v>
       </c>
-      <c r="S5" s="10" t="n">
+      <c r="S5" s="26" t="n">
         <v>46314</v>
       </c>
-      <c r="T5" s="10" t="n">
+      <c r="T5" s="26" t="n">
         <v>46321</v>
       </c>
-      <c r="U5" s="10" t="n">
+      <c r="U5" s="26" t="n">
         <v>46328</v>
       </c>
-      <c r="V5" s="10" t="n">
+      <c r="V5" s="26" t="n">
         <v>46335</v>
       </c>
-      <c r="W5" s="10" t="n">
+      <c r="W5" s="26" t="n">
         <v>46342</v>
       </c>
-      <c r="X5" s="10" t="n">
+      <c r="X5" s="26" t="n">
         <v>46349</v>
       </c>
-      <c r="Y5" s="10" t="n">
+      <c r="Y5" s="26" t="n">
         <v>46356</v>
       </c>
-      <c r="Z5" s="10" t="n">
+      <c r="Z5" s="26" t="n">
         <v>46363</v>
       </c>
-      <c r="AA5" s="10" t="n">
+      <c r="AA5" s="26" t="n">
         <v>46370</v>
       </c>
-      <c r="AB5" s="10" t="n">
+      <c r="AB5" s="26" t="n">
         <v>46377</v>
       </c>
-      <c r="AC5" s="10" t="n">
+      <c r="AC5" s="26" t="n">
         <v>46384</v>
       </c>
     </row>
@@ -1636,7 +1642,11 @@
         <v>0.28</v>
       </c>
       <c r="S19" s="21" t="n"/>
-      <c r="T19" s="21" t="n"/>
+      <c r="T19" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="U19" s="21" t="n"/>
       <c r="V19" s="21" t="n"/>
       <c r="W19" s="21" t="n"/>
@@ -1694,7 +1704,11 @@
           <t>P</t>
         </is>
       </c>
-      <c r="U20" s="21" t="n"/>
+      <c r="U20" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="V20" s="21" t="n"/>
       <c r="W20" s="21" t="n"/>
       <c r="X20" s="21" t="n"/>
@@ -2046,8 +2060,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="U26" s="21" t="n"/>
-      <c r="V26" s="21" t="n"/>
+      <c r="U26" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V26" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="W26" s="21" t="n"/>
       <c r="X26" s="21" t="n"/>
       <c r="Y26" s="21" t="n"/>
@@ -2165,9 +2187,21 @@
       </c>
       <c r="R28" s="21" t="n"/>
       <c r="S28" s="21" t="n"/>
-      <c r="T28" s="21" t="n"/>
-      <c r="U28" s="21" t="n"/>
-      <c r="V28" s="21" t="n"/>
+      <c r="T28" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U28" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V28" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="W28" s="21" t="n"/>
       <c r="X28" s="21" t="n"/>
       <c r="Y28" s="21" t="n"/>
@@ -2281,8 +2315,16 @@
       <c r="S30" s="21" t="n"/>
       <c r="T30" s="21" t="n"/>
       <c r="U30" s="21" t="n"/>
-      <c r="V30" s="21" t="n"/>
-      <c r="W30" s="21" t="n"/>
+      <c r="V30" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W30" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="X30" s="21" t="n"/>
       <c r="Y30" s="21" t="n"/>
       <c r="Z30" s="21" t="n"/>
@@ -3412,9 +3454,21 @@
         <v>0.21</v>
       </c>
       <c r="S51" s="21" t="n"/>
-      <c r="T51" s="21" t="n"/>
-      <c r="U51" s="21" t="n"/>
-      <c r="V51" s="21" t="n"/>
+      <c r="T51" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U51" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V51" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="W51" s="21" t="n"/>
       <c r="X51" s="21" t="n"/>
       <c r="Y51" s="21" t="n"/>
@@ -3472,8 +3526,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="U52" s="21" t="n"/>
-      <c r="V52" s="21" t="n"/>
+      <c r="U52" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V52" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="W52" s="21" t="n"/>
       <c r="X52" s="21" t="n"/>
       <c r="Y52" s="21" t="n"/>
@@ -3531,8 +3593,16 @@
           <t>P</t>
         </is>
       </c>
-      <c r="U53" s="21" t="n"/>
-      <c r="V53" s="21" t="n"/>
+      <c r="U53" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V53" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="W53" s="21" t="n"/>
       <c r="X53" s="21" t="n"/>
       <c r="Y53" s="21" t="n"/>
@@ -4774,8 +4844,16 @@
       <c r="Q77" s="21" t="n"/>
       <c r="R77" s="21" t="n"/>
       <c r="S77" s="21" t="n"/>
-      <c r="T77" s="21" t="n"/>
-      <c r="U77" s="21" t="n"/>
+      <c r="T77" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U77" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="V77" s="21" t="n"/>
       <c r="W77" s="21" t="n"/>
       <c r="X77" s="21" t="n"/>
@@ -4829,8 +4907,16 @@
       <c r="Q78" s="21" t="n"/>
       <c r="R78" s="21" t="n"/>
       <c r="S78" s="21" t="n"/>
-      <c r="T78" s="21" t="n"/>
-      <c r="U78" s="21" t="n"/>
+      <c r="T78" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U78" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="V78" s="21" t="n"/>
       <c r="W78" s="21" t="n"/>
       <c r="X78" s="21" t="n"/>
@@ -4884,8 +4970,16 @@
       <c r="Q79" s="21" t="n"/>
       <c r="R79" s="21" t="n"/>
       <c r="S79" s="21" t="n"/>
-      <c r="T79" s="21" t="n"/>
-      <c r="U79" s="21" t="n"/>
+      <c r="T79" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U79" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="V79" s="21" t="n"/>
       <c r="W79" s="21" t="n"/>
       <c r="X79" s="21" t="n"/>
@@ -4939,8 +5033,16 @@
       <c r="Q80" s="21" t="n"/>
       <c r="R80" s="21" t="n"/>
       <c r="S80" s="21" t="n"/>
-      <c r="T80" s="21" t="n"/>
-      <c r="U80" s="21" t="n"/>
+      <c r="T80" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U80" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="V80" s="21" t="n"/>
       <c r="W80" s="21" t="n"/>
       <c r="X80" s="21" t="n"/>
@@ -4994,8 +5096,16 @@
       <c r="Q81" s="21" t="n"/>
       <c r="R81" s="21" t="n"/>
       <c r="S81" s="21" t="n"/>
-      <c r="T81" s="21" t="n"/>
-      <c r="U81" s="21" t="n"/>
+      <c r="T81" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U81" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="V81" s="21" t="n"/>
       <c r="W81" s="21" t="n"/>
       <c r="X81" s="21" t="n"/>
@@ -5049,8 +5159,16 @@
       <c r="Q82" s="21" t="n"/>
       <c r="R82" s="21" t="n"/>
       <c r="S82" s="21" t="n"/>
-      <c r="T82" s="21" t="n"/>
-      <c r="U82" s="21" t="n"/>
+      <c r="T82" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U82" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="V82" s="21" t="n"/>
       <c r="W82" s="21" t="n"/>
       <c r="X82" s="21" t="n"/>
@@ -5100,7 +5218,11 @@
       <c r="Q83" s="21" t="n"/>
       <c r="R83" s="21" t="n"/>
       <c r="S83" s="21" t="n"/>
-      <c r="T83" s="21" t="n"/>
+      <c r="T83" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="U83" s="21" t="n"/>
       <c r="V83" s="21" t="n"/>
       <c r="W83" s="21" t="n"/>
@@ -5151,7 +5273,11 @@
       <c r="Q84" s="21" t="n"/>
       <c r="R84" s="21" t="n"/>
       <c r="S84" s="21" t="n"/>
-      <c r="T84" s="21" t="n"/>
+      <c r="T84" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="U84" s="21" t="n"/>
       <c r="V84" s="21" t="n"/>
       <c r="W84" s="21" t="n"/>
@@ -5206,8 +5332,16 @@
       <c r="Q85" s="21" t="n"/>
       <c r="R85" s="21" t="n"/>
       <c r="S85" s="21" t="n"/>
-      <c r="T85" s="21" t="n"/>
-      <c r="U85" s="21" t="n"/>
+      <c r="T85" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U85" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="V85" s="21" t="n"/>
       <c r="W85" s="21" t="n"/>
       <c r="X85" s="21" t="n"/>
@@ -5261,8 +5395,16 @@
       <c r="Q86" s="21" t="n"/>
       <c r="R86" s="21" t="n"/>
       <c r="S86" s="21" t="n"/>
-      <c r="T86" s="21" t="n"/>
-      <c r="U86" s="21" t="n"/>
+      <c r="T86" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U86" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="V86" s="21" t="n"/>
       <c r="W86" s="21" t="n"/>
       <c r="X86" s="21" t="n"/>
@@ -5312,7 +5454,11 @@
       <c r="Q87" s="21" t="n"/>
       <c r="R87" s="21" t="n"/>
       <c r="S87" s="21" t="n"/>
-      <c r="T87" s="21" t="n"/>
+      <c r="T87" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="U87" s="21" t="n"/>
       <c r="V87" s="21" t="n"/>
       <c r="W87" s="21" t="n"/>
@@ -5418,10 +5564,26 @@
         </is>
       </c>
       <c r="S89" s="21" t="n"/>
-      <c r="T89" s="21" t="n"/>
-      <c r="U89" s="21" t="n"/>
-      <c r="V89" s="21" t="n"/>
-      <c r="W89" s="21" t="n"/>
+      <c r="T89" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U89" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V89" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W89" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="X89" s="21" t="n"/>
       <c r="Y89" s="21" t="n"/>
       <c r="Z89" s="21" t="n"/>
@@ -5477,9 +5639,21 @@
       </c>
       <c r="R90" s="21" t="n"/>
       <c r="S90" s="21" t="n"/>
-      <c r="T90" s="21" t="n"/>
-      <c r="U90" s="21" t="n"/>
-      <c r="V90" s="21" t="n"/>
+      <c r="T90" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U90" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V90" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="W90" s="21" t="n"/>
       <c r="X90" s="21" t="n"/>
       <c r="Y90" s="21" t="n"/>
@@ -5528,7 +5702,11 @@
       <c r="Q91" s="21" t="n"/>
       <c r="R91" s="21" t="n"/>
       <c r="S91" s="21" t="n"/>
-      <c r="T91" s="21" t="n"/>
+      <c r="T91" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="U91" s="21" t="n"/>
       <c r="V91" s="21" t="n"/>
       <c r="W91" s="21" t="n"/>
@@ -5587,9 +5765,21 @@
       </c>
       <c r="R92" s="21" t="n"/>
       <c r="S92" s="21" t="n"/>
-      <c r="T92" s="21" t="n"/>
-      <c r="U92" s="21" t="n"/>
-      <c r="V92" s="21" t="n"/>
+      <c r="T92" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U92" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="V92" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="W92" s="21" t="n"/>
       <c r="X92" s="21" t="n"/>
       <c r="Y92" s="21" t="n"/>
@@ -5642,8 +5832,16 @@
       <c r="Q93" s="21" t="n"/>
       <c r="R93" s="21" t="n"/>
       <c r="S93" s="21" t="n"/>
-      <c r="T93" s="21" t="n"/>
-      <c r="U93" s="21" t="n"/>
+      <c r="T93" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="U93" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="V93" s="21" t="n"/>
       <c r="W93" s="21" t="n"/>
       <c r="X93" s="21" t="n"/>
@@ -7730,7 +7928,11 @@
       <c r="U133" s="21" t="n"/>
       <c r="V133" s="21" t="n"/>
       <c r="W133" s="21" t="n"/>
-      <c r="X133" s="21" t="n"/>
+      <c r="X133" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Y133" s="21" t="n"/>
       <c r="Z133" s="21" t="n"/>
       <c r="AA133" s="21" t="n"/>
@@ -7781,7 +7983,11 @@
       <c r="U134" s="21" t="n"/>
       <c r="V134" s="21" t="n"/>
       <c r="W134" s="21" t="n"/>
-      <c r="X134" s="21" t="n"/>
+      <c r="X134" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Y134" s="21" t="n"/>
       <c r="Z134" s="21" t="n"/>
       <c r="AA134" s="21" t="n"/>
@@ -7836,8 +8042,16 @@
       <c r="U135" s="21" t="n"/>
       <c r="V135" s="21" t="n"/>
       <c r="W135" s="21" t="n"/>
-      <c r="X135" s="21" t="n"/>
-      <c r="Y135" s="21" t="n"/>
+      <c r="X135" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y135" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Z135" s="21" t="n"/>
       <c r="AA135" s="21" t="n"/>
       <c r="AB135" s="21" t="n"/>
@@ -7887,7 +8101,11 @@
       <c r="U136" s="21" t="n"/>
       <c r="V136" s="21" t="n"/>
       <c r="W136" s="21" t="n"/>
-      <c r="X136" s="21" t="n"/>
+      <c r="X136" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Y136" s="21" t="n"/>
       <c r="Z136" s="21" t="n"/>
       <c r="AA136" s="21" t="n"/>
@@ -7942,8 +8160,16 @@
       <c r="U137" s="21" t="n"/>
       <c r="V137" s="21" t="n"/>
       <c r="W137" s="21" t="n"/>
-      <c r="X137" s="21" t="n"/>
-      <c r="Y137" s="21" t="n"/>
+      <c r="X137" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y137" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Z137" s="21" t="n"/>
       <c r="AA137" s="21" t="n"/>
       <c r="AB137" s="21" t="n"/>
@@ -7993,7 +8219,11 @@
       <c r="U138" s="21" t="n"/>
       <c r="V138" s="21" t="n"/>
       <c r="W138" s="21" t="n"/>
-      <c r="X138" s="21" t="n"/>
+      <c r="X138" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Y138" s="21" t="n"/>
       <c r="Z138" s="21" t="n"/>
       <c r="AA138" s="21" t="n"/>
@@ -8086,7 +8316,11 @@
       <c r="T140" s="21" t="n"/>
       <c r="U140" s="21" t="n"/>
       <c r="V140" s="21" t="n"/>
-      <c r="W140" s="21" t="n"/>
+      <c r="W140" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="X140" s="21" t="n"/>
       <c r="Y140" s="21" t="n"/>
       <c r="Z140" s="21" t="n"/>
@@ -8146,9 +8380,21 @@
       <c r="U141" s="21" t="n"/>
       <c r="V141" s="21" t="n"/>
       <c r="W141" s="21" t="n"/>
-      <c r="X141" s="21" t="n"/>
-      <c r="Y141" s="21" t="n"/>
-      <c r="Z141" s="21" t="n"/>
+      <c r="X141" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Y141" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="Z141" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="AA141" s="21" t="n"/>
       <c r="AB141" s="21" t="n"/>
       <c r="AC141" s="21" t="n"/>
@@ -8198,7 +8444,11 @@
       <c r="V142" s="21" t="n"/>
       <c r="W142" s="21" t="n"/>
       <c r="X142" s="21" t="n"/>
-      <c r="Y142" s="21" t="n"/>
+      <c r="Y142" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Z142" s="21" t="n"/>
       <c r="AA142" s="21" t="n"/>
       <c r="AB142" s="21" t="n"/>
@@ -8249,7 +8499,11 @@
       <c r="V143" s="21" t="n"/>
       <c r="W143" s="21" t="n"/>
       <c r="X143" s="21" t="n"/>
-      <c r="Y143" s="21" t="n"/>
+      <c r="Y143" s="21" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
       <c r="Z143" s="21" t="n"/>
       <c r="AA143" s="21" t="n"/>
       <c r="AB143" s="21" t="n"/>
@@ -8361,109 +8615,110 @@
         <v/>
       </c>
     </row>
+    <row r="146"/>
     <row r="147">
       <c r="B147" s="23" t="inlineStr">
         <is>
           <t>% AVANCE EJECUTADO SEMANAL</t>
         </is>
       </c>
-      <c r="E147" s="24">
+      <c r="E147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,E7:E145)</f>
         <v/>
       </c>
-      <c r="F147" s="24">
+      <c r="F147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,F7:F145)</f>
         <v/>
       </c>
-      <c r="G147" s="24">
+      <c r="G147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,G7:G145)</f>
         <v/>
       </c>
-      <c r="H147" s="24">
+      <c r="H147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,H7:H145)</f>
         <v/>
       </c>
-      <c r="I147" s="24">
+      <c r="I147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,I7:I145)</f>
         <v/>
       </c>
-      <c r="J147" s="24">
+      <c r="J147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,J7:J145)</f>
         <v/>
       </c>
-      <c r="K147" s="24">
+      <c r="K147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,K7:K145)</f>
         <v/>
       </c>
-      <c r="L147" s="24">
+      <c r="L147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,L7:L145)</f>
         <v/>
       </c>
-      <c r="M147" s="24">
+      <c r="M147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,M7:M145)</f>
         <v/>
       </c>
-      <c r="N147" s="24">
+      <c r="N147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,N7:N145)</f>
         <v/>
       </c>
-      <c r="O147" s="24">
+      <c r="O147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,O7:O145)</f>
         <v/>
       </c>
-      <c r="P147" s="24">
+      <c r="P147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,P7:P145)</f>
         <v/>
       </c>
-      <c r="Q147" s="24">
+      <c r="Q147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,Q7:Q145)</f>
         <v/>
       </c>
-      <c r="R147" s="24">
+      <c r="R147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,R7:R145)</f>
         <v/>
       </c>
-      <c r="S147" s="24">
+      <c r="S147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,S7:S145)</f>
         <v/>
       </c>
-      <c r="T147" s="24">
+      <c r="T147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,T7:T145)</f>
         <v/>
       </c>
-      <c r="U147" s="24">
+      <c r="U147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,U7:U145)</f>
         <v/>
       </c>
-      <c r="V147" s="24">
+      <c r="V147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,V7:V145)</f>
         <v/>
       </c>
-      <c r="W147" s="24">
+      <c r="W147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,W7:W145)</f>
         <v/>
       </c>
-      <c r="X147" s="24">
+      <c r="X147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,X7:X145)</f>
         <v/>
       </c>
-      <c r="Y147" s="24">
+      <c r="Y147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,Y7:Y145)</f>
         <v/>
       </c>
-      <c r="Z147" s="24">
+      <c r="Z147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,Z7:Z145)</f>
         <v/>
       </c>
-      <c r="AA147" s="24">
+      <c r="AA147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,AA7:AA145)</f>
         <v/>
       </c>
-      <c r="AB147" s="24">
+      <c r="AB147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,AB7:AB145)</f>
         <v/>
       </c>
-      <c r="AC147" s="24">
+      <c r="AC147" s="27">
         <f>SUMPRODUCT($C$7:$C$145,AC7:AC145)</f>
         <v/>
       </c>
@@ -8474,107 +8729,107 @@
           <t>% AVANCE EJECUTADO ACUMULADO</t>
         </is>
       </c>
-      <c r="E148" s="24">
+      <c r="E148" s="27">
         <f>E147</f>
         <v/>
       </c>
-      <c r="F148" s="24">
+      <c r="F148" s="27">
         <f>E148+F147</f>
         <v/>
       </c>
-      <c r="G148" s="24">
+      <c r="G148" s="27">
         <f>F148+G147</f>
         <v/>
       </c>
-      <c r="H148" s="24">
+      <c r="H148" s="27">
         <f>G148+H147</f>
         <v/>
       </c>
-      <c r="I148" s="24">
+      <c r="I148" s="27">
         <f>H148+I147</f>
         <v/>
       </c>
-      <c r="J148" s="24">
+      <c r="J148" s="27">
         <f>I148+J147</f>
         <v/>
       </c>
-      <c r="K148" s="24">
+      <c r="K148" s="27">
         <f>J148+K147</f>
         <v/>
       </c>
-      <c r="L148" s="24">
+      <c r="L148" s="27">
         <f>K148+L147</f>
         <v/>
       </c>
-      <c r="M148" s="24">
+      <c r="M148" s="27">
         <f>L148+M147</f>
         <v/>
       </c>
-      <c r="N148" s="24">
+      <c r="N148" s="27">
         <f>M148+N147</f>
         <v/>
       </c>
-      <c r="O148" s="24">
+      <c r="O148" s="27">
         <f>N148+O147</f>
         <v/>
       </c>
-      <c r="P148" s="24">
+      <c r="P148" s="27">
         <f>O148+P147</f>
         <v/>
       </c>
-      <c r="Q148" s="24">
+      <c r="Q148" s="27">
         <f>P148+Q147</f>
         <v/>
       </c>
-      <c r="R148" s="24">
+      <c r="R148" s="27">
         <f>Q148+R147</f>
         <v/>
       </c>
-      <c r="S148" s="24">
+      <c r="S148" s="27">
         <f>R148+S147</f>
         <v/>
       </c>
-      <c r="T148" s="24">
+      <c r="T148" s="27">
         <f>S148+T147</f>
         <v/>
       </c>
-      <c r="U148" s="24">
+      <c r="U148" s="27">
         <f>T148+U147</f>
         <v/>
       </c>
-      <c r="V148" s="24">
+      <c r="V148" s="27">
         <f>U148+V147</f>
         <v/>
       </c>
-      <c r="W148" s="24">
+      <c r="W148" s="27">
         <f>V148+W147</f>
         <v/>
       </c>
-      <c r="X148" s="24">
+      <c r="X148" s="27">
         <f>W148+X147</f>
         <v/>
       </c>
-      <c r="Y148" s="24">
+      <c r="Y148" s="27">
         <f>X148+Y147</f>
         <v/>
       </c>
-      <c r="Z148" s="24">
+      <c r="Z148" s="27">
         <f>Y148+Z147</f>
         <v/>
       </c>
-      <c r="AA148" s="24">
+      <c r="AA148" s="27">
         <f>Z148+AA147</f>
         <v/>
       </c>
-      <c r="AB148" s="24">
+      <c r="AB148" s="27">
         <f>AA148+AB147</f>
         <v/>
       </c>
-      <c r="AC148" s="24">
+      <c r="AC148" s="27">
         <f>AB148+AC147</f>
         <v/>
       </c>
-      <c r="AD148" s="25">
+      <c r="AD148" s="28">
         <f>MAX(E148:AC148)</f>
         <v/>
       </c>
@@ -8585,79 +8840,79 @@
           <t>% AVANCE PROGRAMADO SEMANAL (LÍNEA BASE)</t>
         </is>
       </c>
-      <c r="E149" s="24" t="n">
+      <c r="E149" s="27" t="n">
         <v>0.002382311565774134</v>
       </c>
-      <c r="F149" s="24" t="n">
+      <c r="F149" s="27" t="n">
         <v>0.004640837567155562</v>
       </c>
-      <c r="G149" s="24" t="n">
+      <c r="G149" s="27" t="n">
         <v>0.01295631415649645</v>
       </c>
-      <c r="H149" s="24" t="n">
+      <c r="H149" s="27" t="n">
         <v>0.01764782905974209</v>
       </c>
-      <c r="I149" s="24" t="n">
+      <c r="I149" s="27" t="n">
         <v>0.01648804562067233</v>
       </c>
-      <c r="J149" s="24" t="n">
+      <c r="J149" s="27" t="n">
         <v>0.02519193987508428</v>
       </c>
-      <c r="K149" s="24" t="n">
+      <c r="K149" s="27" t="n">
         <v>0.07541910010781293</v>
       </c>
-      <c r="L149" s="24" t="n">
+      <c r="L149" s="27" t="n">
         <v>0.03434983605859502</v>
       </c>
-      <c r="M149" s="24" t="n">
+      <c r="M149" s="27" t="n">
         <v>0.02003410981529835</v>
       </c>
-      <c r="N149" s="24" t="n">
+      <c r="N149" s="27" t="n">
         <v>0.0149819674563707</v>
       </c>
-      <c r="O149" s="24" t="n">
+      <c r="O149" s="27" t="n">
         <v>0.02857673381784588</v>
       </c>
-      <c r="P149" s="24" t="n">
+      <c r="P149" s="27" t="n">
         <v>0.07768505455318526</v>
       </c>
-      <c r="Q149" s="24" t="n">
+      <c r="Q149" s="27" t="n">
         <v>0.04809914053492616</v>
       </c>
-      <c r="R149" s="24" t="n">
+      <c r="R149" s="27" t="n">
         <v>0.0693229330050578</v>
       </c>
-      <c r="S149" s="24" t="n">
+      <c r="S149" s="27" t="n">
         <v>0.06494241547363515</v>
       </c>
-      <c r="T149" s="24" t="n">
+      <c r="T149" s="27" t="n">
         <v>0.06258403049965429</v>
       </c>
-      <c r="U149" s="24" t="n">
+      <c r="U149" s="27" t="n">
         <v>0.06052050055978449</v>
       </c>
-      <c r="V149" s="24" t="n">
+      <c r="V149" s="27" t="n">
         <v>0.06881950213589981</v>
       </c>
-      <c r="W149" s="24" t="n">
+      <c r="W149" s="27" t="n">
         <v>0.05383426486115903</v>
       </c>
-      <c r="X149" s="24" t="n">
+      <c r="X149" s="27" t="n">
         <v>0.05179025604940525</v>
       </c>
-      <c r="Y149" s="24" t="n">
+      <c r="Y149" s="27" t="n">
         <v>0.1489288743837325</v>
       </c>
-      <c r="Z149" s="24" t="n">
+      <c r="Z149" s="27" t="n">
         <v>0.03471030373464231</v>
       </c>
-      <c r="AA149" s="24" t="n">
+      <c r="AA149" s="27" t="n">
         <v>0.002831200276453342</v>
       </c>
-      <c r="AB149" s="24" t="n">
+      <c r="AB149" s="27" t="n">
         <v>0.002330356308297872</v>
       </c>
-      <c r="AC149" s="24" t="n">
+      <c r="AC149" s="27" t="n">
         <v>0.0009321425233191497</v>
       </c>
     </row>
@@ -8667,79 +8922,79 @@
           <t>% AVANCE PROGRAMADO ACUMULADO (LÍNEA BASE)</t>
         </is>
       </c>
-      <c r="E150" s="24" t="n">
+      <c r="E150" s="27" t="n">
         <v>0.002382311565774134</v>
       </c>
-      <c r="F150" s="24" t="n">
+      <c r="F150" s="27" t="n">
         <v>0.007023149132929696</v>
       </c>
-      <c r="G150" s="24" t="n">
+      <c r="G150" s="27" t="n">
         <v>0.01997946328942615</v>
       </c>
-      <c r="H150" s="24" t="n">
+      <c r="H150" s="27" t="n">
         <v>0.03762729234916823</v>
       </c>
-      <c r="I150" s="24" t="n">
+      <c r="I150" s="27" t="n">
         <v>0.05411533796984056</v>
       </c>
-      <c r="J150" s="24" t="n">
+      <c r="J150" s="27" t="n">
         <v>0.07930727784492485</v>
       </c>
-      <c r="K150" s="24" t="n">
+      <c r="K150" s="27" t="n">
         <v>0.1547263779527378</v>
       </c>
-      <c r="L150" s="24" t="n">
+      <c r="L150" s="27" t="n">
         <v>0.1890762140113328</v>
       </c>
-      <c r="M150" s="24" t="n">
+      <c r="M150" s="27" t="n">
         <v>0.2091103238266311</v>
       </c>
-      <c r="N150" s="24" t="n">
+      <c r="N150" s="27" t="n">
         <v>0.2240922912830018</v>
       </c>
-      <c r="O150" s="24" t="n">
+      <c r="O150" s="27" t="n">
         <v>0.2526690251008477</v>
       </c>
-      <c r="P150" s="24" t="n">
+      <c r="P150" s="27" t="n">
         <v>0.330354079654033</v>
       </c>
-      <c r="Q150" s="24" t="n">
+      <c r="Q150" s="27" t="n">
         <v>0.3784532201889591</v>
       </c>
-      <c r="R150" s="24" t="n">
+      <c r="R150" s="27" t="n">
         <v>0.4477761531940169</v>
       </c>
-      <c r="S150" s="24" t="n">
+      <c r="S150" s="27" t="n">
         <v>0.5127185686676521</v>
       </c>
-      <c r="T150" s="24" t="n">
+      <c r="T150" s="27" t="n">
         <v>0.5753025991673064</v>
       </c>
-      <c r="U150" s="24" t="n">
+      <c r="U150" s="27" t="n">
         <v>0.6358230997270909</v>
       </c>
-      <c r="V150" s="24" t="n">
+      <c r="V150" s="27" t="n">
         <v>0.7046426018629908</v>
       </c>
-      <c r="W150" s="24" t="n">
+      <c r="W150" s="27" t="n">
         <v>0.7584768667241498</v>
       </c>
-      <c r="X150" s="24" t="n">
+      <c r="X150" s="27" t="n">
         <v>0.8102671227735551</v>
       </c>
-      <c r="Y150" s="24" t="n">
+      <c r="Y150" s="27" t="n">
         <v>0.9591959971572875</v>
       </c>
-      <c r="Z150" s="24" t="n">
+      <c r="Z150" s="27" t="n">
         <v>0.9939063008919299</v>
       </c>
-      <c r="AA150" s="24" t="n">
+      <c r="AA150" s="27" t="n">
         <v>0.9967375011683832</v>
       </c>
-      <c r="AB150" s="24" t="n">
+      <c r="AB150" s="27" t="n">
         <v>0.9990678574766811</v>
       </c>
-      <c r="AC150" s="24" t="n">
+      <c r="AC150" s="27" t="n">
         <v>1</v>
       </c>
     </row>
